--- a/output/graficos_nacionales/plot_nacional_s_fonasa_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_fonasa_a_2023.xlsx
@@ -15451,7 +15451,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Afiliación FONASA</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_s_fonasa_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_fonasa_a_2023.xlsx
@@ -416,7 +416,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -462,7 +462,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -7684,7 +7684,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -9754,7 +9754,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -10398,7 +10398,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -10582,7 +10582,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -14124,7 +14124,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -14354,7 +14354,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -14722,7 +14722,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -14814,7 +14814,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">

--- a/output/graficos_nacionales/plot_nacional_s_fonasa_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_fonasa_a_2023.xlsx
@@ -2074,7 +2074,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:53</t>
+    <t xml:space="preserve">2026-08-28 15:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_s_fonasa_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_fonasa_a_2023.xlsx
@@ -2074,7 +2074,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 15:11</t>
+    <t xml:space="preserve">2026-08-29 05:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_s_fonasa_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_fonasa_a_2023.xlsx
@@ -2074,7 +2074,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-29 05:47</t>
+    <t xml:space="preserve">2026-09-07 13:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_s_fonasa_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_fonasa_a_2023.xlsx
@@ -2074,7 +2074,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 13:10</t>
+    <t xml:space="preserve">2026-09-08 10:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
